--- a/notes/曾卉购房欠款总账.xlsx
+++ b/notes/曾卉购房欠款总账.xlsx
@@ -40,200 +40,13 @@
     <t xml:space="preserve">剩余</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【湖北农信】尊敬的客户：您在随州农商银行厉山支行尾号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6996</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的贷款于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2022</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日已还本金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">502.4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">元，利息</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">947.62</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">元，合计</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1450.02</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">元，本金余额</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">182318.69</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">元。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">【结清方案】只收 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万，其余一笔勾销（条件：马上一次性付清）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">（日期待定）</t>
+    <t xml:space="preserve">【湖北农信】尊敬的客户：您在随州农商银行厉山支行尾号6996的贷款于2022年4月21日已还本金502.4元，利息947.62元，合计1450.02元，本金余额182318.69元。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【已结清】只收 20 万，其余一笔勾销</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025年初</t>
   </si>
   <si>
     <t xml:space="preserve">豁免</t>
@@ -256,7 +69,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万到账并签结清协议后，债权债务两清，余额为 </t>
+      <t xml:space="preserve">万已于 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年初很快付清，债权债务两清，余额 </t>
     </r>
     <r>
       <rPr>
@@ -267,6 +99,34 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-07-31 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">更新）</t>
     </r>
   </si>
 </sst>
@@ -306,19 +166,20 @@
       <color theme="1"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
-      <name val="等线"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <color theme="1"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -363,24 +224,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,426 +441,426 @@
   <dimension ref="E2:I58"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="2.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="2.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="14.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.5"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>701319</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F3" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>4000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F6" s="0" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F6" s="1" t="n">
         <v>20220111</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>3085.08</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F8" s="0" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F8" s="1" t="n">
         <v>20211211</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="G8" s="1" t="n">
         <v>3085.08</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F9" s="0" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F9" s="1" t="n">
         <v>20211111</v>
       </c>
-      <c r="G9" s="0" t="n">
+      <c r="G9" s="1" t="n">
         <v>3085.08</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="0" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F10" s="1" t="n">
         <v>20211011</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>3085.08</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="0" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F11" s="1" t="n">
         <v>20210911</v>
       </c>
-      <c r="G11" s="0" t="n">
+      <c r="G11" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="0" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F12" s="1" t="n">
         <v>20210811</v>
       </c>
-      <c r="G12" s="0" t="n">
+      <c r="G12" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="0" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F13" s="1" t="n">
         <v>20210711</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="G13" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="0" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F14" s="1" t="n">
         <v>20210611</v>
       </c>
-      <c r="G14" s="0" t="n">
+      <c r="G14" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="0" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F15" s="1" t="n">
         <v>20210511</v>
       </c>
-      <c r="G15" s="0" t="n">
+      <c r="G15" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="0" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F16" s="1" t="n">
         <v>20210414</v>
       </c>
-      <c r="G16" s="0" t="n">
+      <c r="G16" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="0" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F17" s="1" t="n">
         <v>20210311</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="0" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F18" s="1" t="n">
         <v>20210211</v>
       </c>
-      <c r="G18" s="0" t="n">
+      <c r="G18" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F19" s="0" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F19" s="1" t="n">
         <v>20210111</v>
       </c>
-      <c r="G19" s="0" t="n">
+      <c r="G19" s="1" t="n">
         <v>6170.16</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="0" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F21" s="1" t="n">
         <v>20201211</v>
       </c>
-      <c r="G21" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F22" s="0" t="n">
+      <c r="G21" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F22" s="1" t="n">
         <v>20201111</v>
       </c>
-      <c r="G22" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F23" s="0" t="n">
+      <c r="G22" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F23" s="1" t="n">
         <v>20201011</v>
       </c>
-      <c r="G23" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F24" s="0" t="n">
+      <c r="G23" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F24" s="1" t="n">
         <v>20200911</v>
       </c>
-      <c r="G24" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F25" s="0" t="n">
+      <c r="G24" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F25" s="1" t="n">
         <v>20200811</v>
       </c>
-      <c r="G25" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F26" s="0" t="n">
+      <c r="G25" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F26" s="1" t="n">
         <v>20200711</v>
       </c>
-      <c r="G26" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F27" s="0" t="n">
+      <c r="G26" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F27" s="1" t="n">
         <v>20200611</v>
       </c>
-      <c r="G27" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F28" s="0" t="n">
+      <c r="G27" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F28" s="1" t="n">
         <v>20200511</v>
       </c>
-      <c r="G28" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F29" s="0" t="n">
+      <c r="G28" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F29" s="1" t="n">
         <v>20200411</v>
       </c>
-      <c r="G29" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F30" s="0" t="n">
+      <c r="G29" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F30" s="1" t="n">
         <v>20200311</v>
       </c>
-      <c r="G30" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F31" s="0" t="n">
+      <c r="G30" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F31" s="1" t="n">
         <v>20200211</v>
       </c>
-      <c r="G31" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F32" s="0" t="n">
+      <c r="G31" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F32" s="1" t="n">
         <v>20200111</v>
       </c>
-      <c r="G32" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F34" s="0" t="n">
+      <c r="G32" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F34" s="1" t="n">
         <v>20191211</v>
       </c>
-      <c r="G34" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F35" s="0" t="n">
+      <c r="G34" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F35" s="1" t="n">
         <v>20191111</v>
       </c>
-      <c r="G35" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F36" s="0" t="n">
+      <c r="G35" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F36" s="1" t="n">
         <v>20191011</v>
       </c>
-      <c r="G36" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F37" s="0" t="n">
+      <c r="G36" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F37" s="1" t="n">
         <v>20190911</v>
       </c>
-      <c r="G37" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F38" s="0" t="n">
+      <c r="G37" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F38" s="1" t="n">
         <v>20190811</v>
       </c>
-      <c r="G38" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F39" s="0" t="n">
+      <c r="G38" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F39" s="1" t="n">
         <v>20190711</v>
       </c>
-      <c r="G39" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F40" s="0" t="n">
+      <c r="G39" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F40" s="1" t="n">
         <v>20190611</v>
       </c>
-      <c r="G40" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F41" s="0" t="n">
+      <c r="G40" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F41" s="1" t="n">
         <v>20190511</v>
       </c>
-      <c r="G41" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F42" s="0" t="n">
+      <c r="G41" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F42" s="1" t="n">
         <v>20190411</v>
       </c>
-      <c r="G42" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F43" s="0" t="n">
+      <c r="G42" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F43" s="1" t="n">
         <v>20190311</v>
       </c>
-      <c r="G43" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F44" s="0" t="n">
+      <c r="G43" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F44" s="1" t="n">
         <v>20190211</v>
       </c>
-      <c r="G44" s="0" t="n">
-        <v>6235.43</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F45" s="0" t="n">
+      <c r="G44" s="1" t="n">
+        <v>6235.43</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F45" s="1" t="n">
         <v>20190110</v>
       </c>
-      <c r="G45" s="0" t="n">
+      <c r="G45" s="1" t="n">
         <v>10482.1</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F47" s="2" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="G47" s="3" t="n">
         <f aca="false">SUM(G2:G45)</f>
         <v>927087.75</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E49" s="3" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E49" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E50" s="1" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E50" s="2" t="n">
         <v>44645</v>
       </c>
-      <c r="F50" s="0" t="n">
+      <c r="F50" s="1" t="n">
         <v>30000</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="G50" s="3" t="n">
         <f aca="false">G47-F50</f>
         <v>897087.75</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E51" s="1" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E51" s="2" t="n">
         <v>44676</v>
       </c>
-      <c r="F51" s="0" t="n">
+      <c r="F51" s="1" t="n">
         <v>116228.165</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="G51" s="3" t="n">
         <f aca="false">G50-F51</f>
         <v>780859.585</v>
       </c>
-      <c r="I51" s="2" t="s">
+      <c r="I51" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E52" s="1" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E52" s="2" t="n">
         <v>45204</v>
       </c>
-      <c r="F52" s="0" t="n">
+      <c r="F52" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="G52" s="0" t="n">
+      <c r="G52" s="1" t="n">
         <v>680859.6</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E54" s="4" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E54" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E55" s="3" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E55" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E56" s="3" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E56" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F56" s="0" t="n">
+      <c r="F56" s="1" t="n">
         <v>200000</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="G56" s="3" t="n">
         <f aca="false">G52-F56</f>
         <v>480859.6</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E57" s="3" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E57" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="F57" s="3" t="n">
         <f aca="false">G56</f>
         <v>480859.6</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="G57" s="3" t="n">
         <f aca="false">G56-F57</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E58" s="1" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E58" s="2" t="s">
         <v>10</v>
       </c>
     </row>
